--- a/artfynd/S 3399-2025 artfynd.xlsx
+++ b/artfynd/S 3399-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,49 +680,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128438210</v>
+        <v>137524559</v>
       </c>
       <c r="B2" t="n">
-        <v>106813</v>
+        <v>56911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harparbol, 400 m OSO om, Upl</t>
+          <t>Lydinge, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668541</v>
+        <v>668574</v>
       </c>
       <c r="R2" t="n">
-        <v>6649777</v>
+        <v>6649760</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,45 +783,1422 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Lövskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kraftledningsgata</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137524559</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137524561</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56904</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>668574</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6649760</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137524561</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137524558</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56918</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>668574</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6649760</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137524558</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128438210</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Harparbol, 400 m OSO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>668541</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6649777</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Lövskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Thorleif Joelson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Thorleif Joelson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128438210</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137533714</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99461</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>667969</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6649445</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137533714</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137533738</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99461</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>667951</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6649466</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137533738</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137533713</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99716</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>668018</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6649394</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137533713</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137533712</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99244</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>667817</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6649448</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137533712</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137533739</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99244</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>667922</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6649481</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137533739</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137524567</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56911</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>667661</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6649496</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137524567</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137524570</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>667661</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6649496</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137524570</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137524374</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58915</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>667556</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6649458</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137524374</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137524372</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58879</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lydinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>667556</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6649458</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137524372</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
